--- a/docs/po/20102026/GiaiDoan2_Execution_Code_And_Tests/LCMS_TO_BE_Field_Optimization_Inheritance_Matrix_v1.0.xlsx
+++ b/docs/po/20102026/GiaiDoan2_Execution_Code_And_Tests/LCMS_TO_BE_Field_Optimization_Inheritance_Matrix_v1.0.xlsx
@@ -5,7 +5,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Đọc trước" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Ma trận 73 luồng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Kiểm kê 289 trường" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Kiểm kê 293 trường" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 DEV Backlog" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UAT Cases" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 GAP và rủi ro" sheetId="6" state="visible" r:id="rId6"/>
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,6 +137,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5472,7 +5473,7 @@
       </c>
       <c r="N69" s="21" t="inlineStr">
         <is>
-          <t>KHÔNG KẾ THỪA (ĐÚNG THIẾT KẾ GAP-08)</t>
+          <t>ĐÃ KHÓA: KHÔNG KẾ THỪA (PASS UT-22)</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q290"/>
+  <dimension ref="A1:R294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5941,6 +5942,11 @@
       </c>
       <c r="Q1" s="19" t="inlineStr">
         <is>
+          <t>Phân loại Bản chất Trường (GAP-14)</t>
+        </is>
+      </c>
+      <c r="R1" s="19" t="inlineStr">
+        <is>
           <t>Trạng thái TO-BE v1.0</t>
         </is>
       </c>
@@ -6024,7 +6030,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q2" s="20" t="inlineStr">
+      <c r="Q2" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R2" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6109,7 +6120,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q3" s="20" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R3" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6194,7 +6210,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q4" s="20" t="inlineStr">
+      <c r="Q4" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R4" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6279,7 +6300,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q5" s="20" t="inlineStr">
+      <c r="Q5" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R5" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6364,7 +6390,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q6" s="20" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R6" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6449,7 +6480,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q7" s="20" t="inlineStr">
+      <c r="Q7" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R7" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6534,7 +6570,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q8" s="20" t="inlineStr">
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R8" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6619,7 +6660,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q9" s="20" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R9" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6704,7 +6750,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q10" s="20" t="inlineStr">
+      <c r="Q10" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R10" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6789,7 +6840,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q11" s="20" t="inlineStr">
+      <c r="Q11" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R11" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6874,7 +6930,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q12" s="20" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R12" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -6959,7 +7020,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q13" s="20" t="inlineStr">
+      <c r="Q13" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R13" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7044,7 +7110,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q14" s="20" t="inlineStr">
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R14" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7129,7 +7200,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q15" s="20" t="inlineStr">
+      <c r="Q15" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R15" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7214,7 +7290,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q16" s="20" t="inlineStr">
+      <c r="Q16" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R16" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7299,7 +7380,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q17" s="20" t="inlineStr">
+      <c r="Q17" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R17" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7384,7 +7470,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q18" s="20" t="inlineStr">
+      <c r="Q18" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R18" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7469,7 +7560,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q19" s="20" t="inlineStr">
+      <c r="Q19" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R19" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7554,7 +7650,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q20" s="20" t="inlineStr">
+      <c r="Q20" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R20" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7639,7 +7740,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q21" s="20" t="inlineStr">
+      <c r="Q21" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R21" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7724,7 +7830,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q22" s="20" t="inlineStr">
+      <c r="Q22" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R22" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7809,7 +7920,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q23" s="20" t="inlineStr">
+      <c r="Q23" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R23" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7894,7 +8010,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q24" s="20" t="inlineStr">
+      <c r="Q24" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R24" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -7979,7 +8100,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q25" s="20" t="inlineStr">
+      <c r="Q25" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R25" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8064,7 +8190,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q26" s="20" t="inlineStr">
+      <c r="Q26" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R26" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8149,7 +8280,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q27" s="20" t="inlineStr">
+      <c r="Q27" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R27" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8234,7 +8370,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q28" s="20" t="inlineStr">
+      <c r="Q28" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R28" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8319,7 +8460,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q29" s="20" t="inlineStr">
+      <c r="Q29" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R29" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8404,7 +8550,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q30" s="20" t="inlineStr">
+      <c r="Q30" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R30" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8489,7 +8640,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q31" s="20" t="inlineStr">
+      <c r="Q31" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R31" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8574,7 +8730,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q32" s="20" t="inlineStr">
+      <c r="Q32" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R32" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8659,7 +8820,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q33" s="20" t="inlineStr">
+      <c r="Q33" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R33" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8744,7 +8910,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q34" s="20" t="inlineStr">
+      <c r="Q34" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R34" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8829,7 +9000,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q35" s="20" t="inlineStr">
+      <c r="Q35" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R35" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8914,7 +9090,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q36" s="20" t="inlineStr">
+      <c r="Q36" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R36" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -8999,7 +9180,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q37" s="20" t="inlineStr">
+      <c r="Q37" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R37" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9084,7 +9270,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q38" s="20" t="inlineStr">
+      <c r="Q38" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R38" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9169,7 +9360,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q39" s="20" t="inlineStr">
+      <c r="Q39" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R39" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9254,7 +9450,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q40" s="20" t="inlineStr">
+      <c r="Q40" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R40" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9339,7 +9540,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q41" s="20" t="inlineStr">
+      <c r="Q41" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R41" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9424,7 +9630,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q42" s="20" t="inlineStr">
+      <c r="Q42" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R42" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9509,7 +9720,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q43" s="20" t="inlineStr">
+      <c r="Q43" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R43" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9594,7 +9810,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q44" s="20" t="inlineStr">
+      <c r="Q44" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R44" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9679,7 +9900,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q45" s="20" t="inlineStr">
+      <c r="Q45" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R45" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9764,7 +9990,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q46" s="20" t="inlineStr">
+      <c r="Q46" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R46" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9849,7 +10080,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q47" s="20" t="inlineStr">
+      <c r="Q47" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R47" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -9934,7 +10170,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q48" s="20" t="inlineStr">
+      <c r="Q48" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R48" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10019,7 +10260,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q49" s="20" t="inlineStr">
+      <c r="Q49" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R49" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10104,7 +10350,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q50" s="20" t="inlineStr">
+      <c r="Q50" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R50" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10189,7 +10440,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q51" s="20" t="inlineStr">
+      <c r="Q51" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R51" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10274,7 +10530,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q52" s="20" t="inlineStr">
+      <c r="Q52" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R52" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10359,7 +10620,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q53" s="20" t="inlineStr">
+      <c r="Q53" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R53" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10444,7 +10710,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q54" s="20" t="inlineStr">
+      <c r="Q54" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R54" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10529,7 +10800,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q55" s="20" t="inlineStr">
+      <c r="Q55" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R55" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10614,7 +10890,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q56" s="20" t="inlineStr">
+      <c r="Q56" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R56" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10699,7 +10980,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q57" s="20" t="inlineStr">
+      <c r="Q57" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R57" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10784,7 +11070,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q58" s="20" t="inlineStr">
+      <c r="Q58" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R58" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10869,7 +11160,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q59" s="20" t="inlineStr">
+      <c r="Q59" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R59" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -10954,7 +11250,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q60" s="20" t="inlineStr">
+      <c r="Q60" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R60" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11039,7 +11340,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q61" s="20" t="inlineStr">
+      <c r="Q61" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R61" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11124,7 +11430,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q62" s="20" t="inlineStr">
+      <c r="Q62" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R62" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11209,7 +11520,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q63" s="20" t="inlineStr">
+      <c r="Q63" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R63" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11294,7 +11610,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q64" s="20" t="inlineStr">
+      <c r="Q64" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R64" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11379,7 +11700,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q65" s="20" t="inlineStr">
+      <c r="Q65" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R65" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11464,7 +11790,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q66" s="20" t="inlineStr">
+      <c r="Q66" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R66" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11549,7 +11880,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q67" s="20" t="inlineStr">
+      <c r="Q67" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R67" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11634,7 +11970,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q68" s="20" t="inlineStr">
+      <c r="Q68" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R68" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11719,7 +12060,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q69" s="20" t="inlineStr">
+      <c r="Q69" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R69" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11804,7 +12150,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q70" s="20" t="inlineStr">
+      <c r="Q70" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R70" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11889,7 +12240,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q71" s="20" t="inlineStr">
+      <c r="Q71" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R71" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -11974,7 +12330,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q72" s="20" t="inlineStr">
+      <c r="Q72" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R72" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12059,7 +12420,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q73" s="20" t="inlineStr">
+      <c r="Q73" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R73" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12144,7 +12510,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q74" s="20" t="inlineStr">
+      <c r="Q74" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R74" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12229,7 +12600,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q75" s="20" t="inlineStr">
+      <c r="Q75" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R75" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12314,7 +12690,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q76" s="20" t="inlineStr">
+      <c r="Q76" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R76" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12399,7 +12780,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q77" s="20" t="inlineStr">
+      <c r="Q77" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R77" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12484,7 +12870,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q78" s="20" t="inlineStr">
+      <c r="Q78" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R78" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12569,7 +12960,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q79" s="20" t="inlineStr">
+      <c r="Q79" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R79" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12654,7 +13050,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q80" s="20" t="inlineStr">
+      <c r="Q80" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R80" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12739,7 +13140,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q81" s="20" t="inlineStr">
+      <c r="Q81" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R81" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12824,7 +13230,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q82" s="20" t="inlineStr">
+      <c r="Q82" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R82" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12909,7 +13320,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q83" s="20" t="inlineStr">
+      <c r="Q83" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R83" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -12994,7 +13410,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q84" s="20" t="inlineStr">
+      <c r="Q84" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R84" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13079,7 +13500,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q85" s="20" t="inlineStr">
+      <c r="Q85" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R85" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13164,7 +13590,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q86" s="20" t="inlineStr">
+      <c r="Q86" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R86" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13249,7 +13680,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q87" s="20" t="inlineStr">
+      <c r="Q87" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R87" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13334,7 +13770,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q88" s="20" t="inlineStr">
+      <c r="Q88" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R88" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13419,7 +13860,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q89" s="20" t="inlineStr">
+      <c r="Q89" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R89" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13504,7 +13950,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q90" s="20" t="inlineStr">
+      <c r="Q90" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R90" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13589,7 +14040,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q91" s="20" t="inlineStr">
+      <c r="Q91" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R91" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13674,7 +14130,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q92" s="20" t="inlineStr">
+      <c r="Q92" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R92" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13759,7 +14220,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q93" s="20" t="inlineStr">
+      <c r="Q93" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R93" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13844,7 +14310,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q94" s="20" t="inlineStr">
+      <c r="Q94" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R94" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -13929,7 +14400,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q95" s="20" t="inlineStr">
+      <c r="Q95" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R95" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14014,7 +14490,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q96" s="20" t="inlineStr">
+      <c r="Q96" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R96" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14099,7 +14580,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q97" s="20" t="inlineStr">
+      <c r="Q97" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R97" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14184,7 +14670,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q98" s="20" t="inlineStr">
+      <c r="Q98" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R98" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14269,7 +14760,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q99" s="20" t="inlineStr">
+      <c r="Q99" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R99" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14354,7 +14850,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q100" s="20" t="inlineStr">
+      <c r="Q100" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R100" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14439,7 +14940,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q101" s="20" t="inlineStr">
+      <c r="Q101" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R101" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14524,7 +15030,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q102" s="20" t="inlineStr">
+      <c r="Q102" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R102" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14609,7 +15120,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q103" s="20" t="inlineStr">
+      <c r="Q103" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R103" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14694,7 +15210,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q104" s="20" t="inlineStr">
+      <c r="Q104" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R104" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14779,7 +15300,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q105" s="20" t="inlineStr">
+      <c r="Q105" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R105" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14864,7 +15390,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q106" s="20" t="inlineStr">
+      <c r="Q106" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R106" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -14949,7 +15480,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q107" s="20" t="inlineStr">
+      <c r="Q107" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R107" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15034,7 +15570,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q108" s="20" t="inlineStr">
+      <c r="Q108" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R108" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15119,7 +15660,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q109" s="20" t="inlineStr">
+      <c r="Q109" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R109" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15204,7 +15750,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q110" s="20" t="inlineStr">
+      <c r="Q110" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R110" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15289,7 +15840,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q111" s="20" t="inlineStr">
+      <c r="Q111" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R111" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15374,7 +15930,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q112" s="20" t="inlineStr">
+      <c r="Q112" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R112" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15459,7 +16020,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q113" s="20" t="inlineStr">
+      <c r="Q113" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R113" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15544,7 +16110,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q114" s="20" t="inlineStr">
+      <c r="Q114" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R114" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15629,7 +16200,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q115" s="20" t="inlineStr">
+      <c r="Q115" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R115" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15714,7 +16290,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q116" s="20" t="inlineStr">
+      <c r="Q116" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R116" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15799,7 +16380,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q117" s="20" t="inlineStr">
+      <c r="Q117" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R117" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15884,7 +16470,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q118" s="20" t="inlineStr">
+      <c r="Q118" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R118" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -15969,7 +16560,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q119" s="20" t="inlineStr">
+      <c r="Q119" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R119" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16054,7 +16650,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q120" s="20" t="inlineStr">
+      <c r="Q120" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R120" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16139,7 +16740,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q121" s="20" t="inlineStr">
+      <c r="Q121" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R121" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16224,7 +16830,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q122" s="20" t="inlineStr">
+      <c r="Q122" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R122" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16309,7 +16920,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q123" s="20" t="inlineStr">
+      <c r="Q123" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R123" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16394,7 +17010,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q124" s="20" t="inlineStr">
+      <c r="Q124" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R124" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16479,7 +17100,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q125" s="20" t="inlineStr">
+      <c r="Q125" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R125" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16564,7 +17190,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q126" s="20" t="inlineStr">
+      <c r="Q126" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R126" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16649,7 +17280,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q127" s="20" t="inlineStr">
+      <c r="Q127" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R127" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16734,7 +17370,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q128" s="20" t="inlineStr">
+      <c r="Q128" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R128" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16819,7 +17460,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q129" s="20" t="inlineStr">
+      <c r="Q129" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R129" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16904,7 +17550,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q130" s="20" t="inlineStr">
+      <c r="Q130" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R130" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -16989,7 +17640,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q131" s="20" t="inlineStr">
+      <c r="Q131" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R131" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17074,7 +17730,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q132" s="20" t="inlineStr">
+      <c r="Q132" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R132" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17159,7 +17820,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q133" s="20" t="inlineStr">
+      <c r="Q133" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R133" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17244,7 +17910,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q134" s="20" t="inlineStr">
+      <c r="Q134" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R134" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17329,7 +18000,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q135" s="20" t="inlineStr">
+      <c r="Q135" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R135" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17414,7 +18090,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q136" s="20" t="inlineStr">
+      <c r="Q136" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R136" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17499,7 +18180,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q137" s="20" t="inlineStr">
+      <c r="Q137" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R137" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17584,7 +18270,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q138" s="20" t="inlineStr">
+      <c r="Q138" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R138" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17669,7 +18360,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q139" s="20" t="inlineStr">
+      <c r="Q139" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R139" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17754,7 +18450,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q140" s="20" t="inlineStr">
+      <c r="Q140" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R140" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17839,7 +18540,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q141" s="20" t="inlineStr">
+      <c r="Q141" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R141" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -17924,7 +18630,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q142" s="20" t="inlineStr">
+      <c r="Q142" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R142" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18009,7 +18720,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q143" s="20" t="inlineStr">
+      <c r="Q143" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R143" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18094,7 +18810,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q144" s="20" t="inlineStr">
+      <c r="Q144" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R144" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18179,7 +18900,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q145" s="20" t="inlineStr">
+      <c r="Q145" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R145" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18264,7 +18990,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q146" s="20" t="inlineStr">
+      <c r="Q146" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R146" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18349,7 +19080,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q147" s="20" t="inlineStr">
+      <c r="Q147" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R147" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18434,7 +19170,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q148" s="20" t="inlineStr">
+      <c r="Q148" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R148" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18519,7 +19260,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q149" s="20" t="inlineStr">
+      <c r="Q149" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R149" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18604,7 +19350,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q150" s="20" t="inlineStr">
+      <c r="Q150" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R150" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18689,7 +19440,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q151" s="20" t="inlineStr">
+      <c r="Q151" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R151" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18774,7 +19530,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q152" s="20" t="inlineStr">
+      <c r="Q152" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R152" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18859,7 +19620,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q153" s="20" t="inlineStr">
+      <c r="Q153" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R153" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -18944,7 +19710,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q154" s="20" t="inlineStr">
+      <c r="Q154" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R154" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19029,7 +19800,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q155" s="20" t="inlineStr">
+      <c r="Q155" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R155" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19114,7 +19890,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q156" s="20" t="inlineStr">
+      <c r="Q156" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R156" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19199,7 +19980,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q157" s="20" t="inlineStr">
+      <c r="Q157" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R157" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19284,7 +20070,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q158" s="20" t="inlineStr">
+      <c r="Q158" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R158" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19369,7 +20160,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q159" s="20" t="inlineStr">
+      <c r="Q159" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R159" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19454,7 +20250,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q160" s="20" t="inlineStr">
+      <c r="Q160" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R160" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19539,7 +20340,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q161" s="20" t="inlineStr">
+      <c r="Q161" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R161" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19624,7 +20430,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q162" s="20" t="inlineStr">
+      <c r="Q162" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R162" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19709,7 +20520,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q163" s="20" t="inlineStr">
+      <c r="Q163" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R163" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19794,7 +20610,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q164" s="20" t="inlineStr">
+      <c r="Q164" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R164" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19879,7 +20700,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q165" s="20" t="inlineStr">
+      <c r="Q165" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R165" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -19964,7 +20790,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q166" s="20" t="inlineStr">
+      <c r="Q166" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R166" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20049,7 +20880,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q167" s="20" t="inlineStr">
+      <c r="Q167" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R167" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20134,7 +20970,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q168" s="20" t="inlineStr">
+      <c r="Q168" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R168" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20219,7 +21060,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q169" s="20" t="inlineStr">
+      <c r="Q169" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R169" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20304,7 +21150,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q170" s="20" t="inlineStr">
+      <c r="Q170" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R170" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20389,7 +21240,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q171" s="20" t="inlineStr">
+      <c r="Q171" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R171" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20474,7 +21330,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q172" s="20" t="inlineStr">
+      <c r="Q172" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R172" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20559,7 +21420,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q173" s="20" t="inlineStr">
+      <c r="Q173" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R173" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20644,7 +21510,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q174" s="20" t="inlineStr">
+      <c r="Q174" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R174" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20729,7 +21600,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q175" s="20" t="inlineStr">
+      <c r="Q175" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R175" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20814,7 +21690,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q176" s="20" t="inlineStr">
+      <c r="Q176" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R176" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20899,7 +21780,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q177" s="20" t="inlineStr">
+      <c r="Q177" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R177" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -20984,7 +21870,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q178" s="20" t="inlineStr">
+      <c r="Q178" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R178" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21069,7 +21960,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q179" s="20" t="inlineStr">
+      <c r="Q179" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R179" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21154,7 +22050,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q180" s="20" t="inlineStr">
+      <c r="Q180" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R180" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21239,7 +22140,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q181" s="20" t="inlineStr">
+      <c r="Q181" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R181" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21324,7 +22230,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q182" s="20" t="inlineStr">
+      <c r="Q182" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R182" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21409,7 +22320,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q183" s="20" t="inlineStr">
+      <c r="Q183" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R183" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21494,7 +22410,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q184" s="20" t="inlineStr">
+      <c r="Q184" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R184" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21579,7 +22500,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q185" s="20" t="inlineStr">
+      <c r="Q185" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R185" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21664,7 +22590,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q186" s="20" t="inlineStr">
+      <c r="Q186" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R186" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21749,7 +22680,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q187" s="20" t="inlineStr">
+      <c r="Q187" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R187" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21834,7 +22770,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q188" s="20" t="inlineStr">
+      <c r="Q188" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R188" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -21919,7 +22860,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q189" s="20" t="inlineStr">
+      <c r="Q189" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R189" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22004,7 +22950,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q190" s="20" t="inlineStr">
+      <c r="Q190" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R190" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22089,7 +23040,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q191" s="20" t="inlineStr">
+      <c r="Q191" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R191" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22174,7 +23130,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q192" s="20" t="inlineStr">
+      <c r="Q192" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R192" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22259,7 +23220,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q193" s="20" t="inlineStr">
+      <c r="Q193" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R193" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22344,7 +23310,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q194" s="20" t="inlineStr">
+      <c r="Q194" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R194" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22429,7 +23400,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q195" s="20" t="inlineStr">
+      <c r="Q195" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R195" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22514,7 +23490,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q196" s="20" t="inlineStr">
+      <c r="Q196" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R196" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22599,7 +23580,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q197" s="20" t="inlineStr">
+      <c r="Q197" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R197" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22684,7 +23670,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q198" s="20" t="inlineStr">
+      <c r="Q198" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R198" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22769,7 +23760,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q199" s="20" t="inlineStr">
+      <c r="Q199" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R199" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22854,7 +23850,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q200" s="20" t="inlineStr">
+      <c r="Q200" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R200" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -22939,7 +23940,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q201" s="20" t="inlineStr">
+      <c r="Q201" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R201" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23024,7 +24030,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q202" s="20" t="inlineStr">
+      <c r="Q202" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R202" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23109,7 +24120,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q203" s="20" t="inlineStr">
+      <c r="Q203" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R203" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23194,7 +24210,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q204" s="20" t="inlineStr">
+      <c r="Q204" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R204" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23279,7 +24300,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q205" s="20" t="inlineStr">
+      <c r="Q205" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R205" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23364,7 +24390,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q206" s="20" t="inlineStr">
+      <c r="Q206" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R206" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23449,7 +24480,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q207" s="20" t="inlineStr">
+      <c r="Q207" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R207" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23534,7 +24570,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q208" s="20" t="inlineStr">
+      <c r="Q208" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R208" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23619,7 +24660,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q209" s="20" t="inlineStr">
+      <c r="Q209" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R209" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23704,7 +24750,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q210" s="20" t="inlineStr">
+      <c r="Q210" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R210" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23789,7 +24840,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q211" s="20" t="inlineStr">
+      <c r="Q211" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R211" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23874,7 +24930,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q212" s="20" t="inlineStr">
+      <c r="Q212" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R212" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -23959,7 +25020,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q213" s="20" t="inlineStr">
+      <c r="Q213" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R213" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24044,7 +25110,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q214" s="20" t="inlineStr">
+      <c r="Q214" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R214" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24129,7 +25200,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q215" s="20" t="inlineStr">
+      <c r="Q215" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R215" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24214,7 +25290,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q216" s="20" t="inlineStr">
+      <c r="Q216" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R216" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24299,7 +25380,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q217" s="20" t="inlineStr">
+      <c r="Q217" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R217" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24384,7 +25470,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q218" s="20" t="inlineStr">
+      <c r="Q218" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R218" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24469,7 +25560,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q219" s="20" t="inlineStr">
+      <c r="Q219" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R219" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24554,7 +25650,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q220" s="20" t="inlineStr">
+      <c r="Q220" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R220" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24639,7 +25740,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q221" s="20" t="inlineStr">
+      <c r="Q221" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R221" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24724,7 +25830,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q222" s="20" t="inlineStr">
+      <c r="Q222" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R222" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24809,7 +25920,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q223" s="20" t="inlineStr">
+      <c r="Q223" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R223" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24894,7 +26010,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q224" s="20" t="inlineStr">
+      <c r="Q224" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R224" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -24979,7 +26100,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q225" s="20" t="inlineStr">
+      <c r="Q225" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R225" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25064,7 +26190,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q226" s="20" t="inlineStr">
+      <c r="Q226" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R226" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25149,7 +26280,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q227" s="20" t="inlineStr">
+      <c r="Q227" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R227" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25234,7 +26370,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q228" s="20" t="inlineStr">
+      <c r="Q228" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R228" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25319,7 +26460,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q229" s="20" t="inlineStr">
+      <c r="Q229" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R229" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25404,7 +26550,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q230" s="20" t="inlineStr">
+      <c r="Q230" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R230" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25489,7 +26640,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q231" s="20" t="inlineStr">
+      <c r="Q231" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R231" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25574,7 +26730,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q232" s="20" t="inlineStr">
+      <c r="Q232" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R232" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25659,7 +26820,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q233" s="20" t="inlineStr">
+      <c r="Q233" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R233" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25744,7 +26910,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q234" s="20" t="inlineStr">
+      <c r="Q234" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R234" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25829,7 +27000,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q235" s="20" t="inlineStr">
+      <c r="Q235" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R235" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25914,7 +27090,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q236" s="20" t="inlineStr">
+      <c r="Q236" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R236" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -25999,7 +27180,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q237" s="20" t="inlineStr">
+      <c r="Q237" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R237" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26084,7 +27270,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q238" s="20" t="inlineStr">
+      <c r="Q238" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R238" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26169,7 +27360,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q239" s="20" t="inlineStr">
+      <c r="Q239" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R239" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26254,7 +27450,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q240" s="20" t="inlineStr">
+      <c r="Q240" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R240" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26339,7 +27540,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q241" s="20" t="inlineStr">
+      <c r="Q241" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R241" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26424,7 +27630,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q242" s="20" t="inlineStr">
+      <c r="Q242" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R242" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26509,7 +27720,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q243" s="20" t="inlineStr">
+      <c r="Q243" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R243" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26594,7 +27810,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q244" s="20" t="inlineStr">
+      <c r="Q244" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R244" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26679,7 +27900,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q245" s="20" t="inlineStr">
+      <c r="Q245" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R245" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26764,7 +27990,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q246" s="20" t="inlineStr">
+      <c r="Q246" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R246" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26849,7 +28080,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q247" s="20" t="inlineStr">
+      <c r="Q247" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R247" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -26934,7 +28170,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q248" s="20" t="inlineStr">
+      <c r="Q248" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R248" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27019,7 +28260,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q249" s="20" t="inlineStr">
+      <c r="Q249" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R249" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27104,7 +28350,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q250" s="20" t="inlineStr">
+      <c r="Q250" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R250" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27189,7 +28440,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q251" s="20" t="inlineStr">
+      <c r="Q251" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R251" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27274,7 +28530,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q252" s="20" t="inlineStr">
+      <c r="Q252" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R252" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27359,7 +28620,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q253" s="20" t="inlineStr">
+      <c r="Q253" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R253" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27444,7 +28710,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q254" s="20" t="inlineStr">
+      <c r="Q254" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R254" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27529,7 +28800,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q255" s="20" t="inlineStr">
+      <c r="Q255" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R255" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27614,7 +28890,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q256" s="20" t="inlineStr">
+      <c r="Q256" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R256" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27699,7 +28980,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q257" s="20" t="inlineStr">
+      <c r="Q257" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R257" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27784,7 +29070,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q258" s="20" t="inlineStr">
+      <c r="Q258" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R258" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27869,7 +29160,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q259" s="20" t="inlineStr">
+      <c r="Q259" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R259" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -27954,7 +29250,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q260" s="20" t="inlineStr">
+      <c r="Q260" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R260" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28039,7 +29340,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q261" s="20" t="inlineStr">
+      <c r="Q261" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R261" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28124,7 +29430,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q262" s="20" t="inlineStr">
+      <c r="Q262" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R262" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28209,7 +29520,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q263" s="20" t="inlineStr">
+      <c r="Q263" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R263" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28294,7 +29610,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q264" s="20" t="inlineStr">
+      <c r="Q264" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R264" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28379,7 +29700,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q265" s="20" t="inlineStr">
+      <c r="Q265" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R265" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28464,7 +29790,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q266" s="20" t="inlineStr">
+      <c r="Q266" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R266" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28549,7 +29880,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q267" s="20" t="inlineStr">
+      <c r="Q267" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R267" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28634,7 +29970,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q268" s="20" t="inlineStr">
+      <c r="Q268" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R268" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28719,7 +30060,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q269" s="20" t="inlineStr">
+      <c r="Q269" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R269" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28804,7 +30150,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q270" s="20" t="inlineStr">
+      <c r="Q270" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R270" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28889,7 +30240,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q271" s="20" t="inlineStr">
+      <c r="Q271" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R271" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -28974,7 +30330,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q272" s="20" t="inlineStr">
+      <c r="Q272" s="22" t="inlineStr">
+        <is>
+          <t>5. Chỉ đọc / Trạng thái</t>
+        </is>
+      </c>
+      <c r="R272" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29059,7 +30420,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q273" s="20" t="inlineStr">
+      <c r="Q273" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R273" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29144,7 +30510,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q274" s="20" t="inlineStr">
+      <c r="Q274" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R274" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29229,7 +30600,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q275" s="20" t="inlineStr">
+      <c r="Q275" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R275" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29314,7 +30690,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q276" s="20" t="inlineStr">
+      <c r="Q276" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R276" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29399,7 +30780,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q277" s="20" t="inlineStr">
+      <c r="Q277" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R277" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29484,7 +30870,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q278" s="20" t="inlineStr">
+      <c r="Q278" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R278" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29569,7 +30960,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q279" s="20" t="inlineStr">
+      <c r="Q279" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R279" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29654,7 +31050,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q280" s="20" t="inlineStr">
+      <c r="Q280" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R280" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29739,7 +31140,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q281" s="20" t="inlineStr">
+      <c r="Q281" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R281" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29824,7 +31230,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q282" s="20" t="inlineStr">
+      <c r="Q282" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R282" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29909,7 +31320,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q283" s="20" t="inlineStr">
+      <c r="Q283" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R283" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -29994,7 +31410,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q284" s="20" t="inlineStr">
+      <c r="Q284" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R284" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -30079,7 +31500,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q285" s="20" t="inlineStr">
+      <c r="Q285" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R285" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -30164,7 +31590,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q286" s="20" t="inlineStr">
+      <c r="Q286" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R286" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -30249,7 +31680,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q287" s="20" t="inlineStr">
+      <c r="Q287" s="22" t="inlineStr">
+        <is>
+          <t>2. Chọn danh mục chuẩn</t>
+        </is>
+      </c>
+      <c r="R287" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -30334,7 +31770,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q288" s="20" t="inlineStr">
+      <c r="Q288" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R288" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -30419,7 +31860,12 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q289" s="20" t="inlineStr">
+      <c r="Q289" s="22" t="inlineStr">
+        <is>
+          <t>1. Nhập tay nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="R289" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -30504,7 +31950,372 @@
           <t>BA TO-BE ĐỀ XUẤT</t>
         </is>
       </c>
-      <c r="Q290" s="20" t="inlineStr">
+      <c r="Q290" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R290" s="20" t="inlineStr">
+        <is>
+          <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="22" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="22" t="inlineStr">
+        <is>
+          <t>Vận hành (Operations)</t>
+        </is>
+      </c>
+      <c r="C291" s="22" t="inlineStr">
+        <is>
+          <t>Tạo mới &amp; Chi tiết Chặng vận chuyển (/operations/legs/new, /operations/legs/[id])</t>
+        </is>
+      </c>
+      <c r="D291" s="22" t="inlineStr">
+        <is>
+          <t>Trọng lượng thực chặng (Gross Weight Kg) *</t>
+        </is>
+      </c>
+      <c r="E291" s="22" t="inlineStr">
+        <is>
+          <t>grossWeightKg</t>
+        </is>
+      </c>
+      <c r="F291" s="22" t="inlineStr">
+        <is>
+          <t>transport_legs.gross_weight_kg</t>
+        </is>
+      </c>
+      <c r="G291" s="22" t="inlineStr">
+        <is>
+          <t>Optional / Required khi rating chặng (GAP-12)</t>
+        </is>
+      </c>
+      <c r="H291" s="22" t="inlineStr">
+        <is>
+          <t>Nhập số / Kế thừa đo lường chặng</t>
+        </is>
+      </c>
+      <c r="I291" s="22" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J291" s="22" t="inlineStr">
+        <is>
+          <t>Hệ thống vận hành (Ops SoT / Transport Leg)</t>
+        </is>
+      </c>
+      <c r="K291" s="22" t="inlineStr">
+        <is>
+          <t>KẾ THỪA / NHẬP TAY CHẶNG</t>
+        </is>
+      </c>
+      <c r="L291" s="22" t="inlineStr">
+        <is>
+          <t>Bắt buộc có trọng lượng riêng của chặng khi tính giá chặng (UT-14); cấm mượn trọng lượng Bill.</t>
+        </is>
+      </c>
+      <c r="M291" s="22" t="inlineStr">
+        <is>
+          <t>Luồng 4 (Shipment -&gt; Leg) &amp; UT-14</t>
+        </is>
+      </c>
+      <c r="N291" s="22" t="inlineStr">
+        <is>
+          <t>Dùng trực tiếp tính giá cước Chặng (Buy Leg Rating)</t>
+        </is>
+      </c>
+      <c r="O291" s="22" t="inlineStr">
+        <is>
+          <t>UI: LegDetail.tsx; API: UpsertTransportLegRequest; DB: transport_legs (migration 20261013065435_TransportLegBuyInputs); Test: UT14</t>
+        </is>
+      </c>
+      <c r="P291" s="22" t="inlineStr">
+        <is>
+          <t>ĐÃ BỔ SUNG THEO GAP-12</t>
+        </is>
+      </c>
+      <c r="Q291" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R291" s="20" t="inlineStr">
+        <is>
+          <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="22" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="22" t="inlineStr">
+        <is>
+          <t>Vận hành (Operations)</t>
+        </is>
+      </c>
+      <c r="C292" s="22" t="inlineStr">
+        <is>
+          <t>Tạo mới &amp; Chi tiết Chặng vận chuyển (/operations/legs/new, /operations/legs/[id])</t>
+        </is>
+      </c>
+      <c r="D292" s="22" t="inlineStr">
+        <is>
+          <t>Thể tích chặng (Volume CBM)</t>
+        </is>
+      </c>
+      <c r="E292" s="22" t="inlineStr">
+        <is>
+          <t>volumeCbm</t>
+        </is>
+      </c>
+      <c r="F292" s="22" t="inlineStr">
+        <is>
+          <t>transport_legs.volume_cbm</t>
+        </is>
+      </c>
+      <c r="G292" s="22" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H292" s="22" t="inlineStr">
+        <is>
+          <t>Nhập số / Kế thừa đo lường chặng</t>
+        </is>
+      </c>
+      <c r="I292" s="22" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J292" s="22" t="inlineStr">
+        <is>
+          <t>Hệ thống vận hành (Ops SoT / Transport Leg)</t>
+        </is>
+      </c>
+      <c r="K292" s="22" t="inlineStr">
+        <is>
+          <t>KẾ THỪA / NHẬP TAY CHẶNG</t>
+        </is>
+      </c>
+      <c r="L292" s="22" t="inlineStr">
+        <is>
+          <t>Kế thừa từ đo lường thực tế của chặng phục vụ quy đổi thể tích.</t>
+        </is>
+      </c>
+      <c r="M292" s="22" t="inlineStr">
+        <is>
+          <t>Luồng 4 (Shipment -&gt; Leg) &amp; UT-14</t>
+        </is>
+      </c>
+      <c r="N292" s="22" t="inlineStr">
+        <is>
+          <t>Dùng tính giá chặng theo CBM hoặc W/M</t>
+        </is>
+      </c>
+      <c r="O292" s="22" t="inlineStr">
+        <is>
+          <t>UI: LegDetail.tsx; API: UpsertTransportLegRequest; DB: transport_legs (migration 20261013065435_TransportLegBuyInputs); Test: UT14</t>
+        </is>
+      </c>
+      <c r="P292" s="22" t="inlineStr">
+        <is>
+          <t>ĐÃ BỔ SUNG THEO GAP-12</t>
+        </is>
+      </c>
+      <c r="Q292" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R292" s="20" t="inlineStr">
+        <is>
+          <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="22" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="22" t="inlineStr">
+        <is>
+          <t>Vận hành (Operations)</t>
+        </is>
+      </c>
+      <c r="C293" s="22" t="inlineStr">
+        <is>
+          <t>Tạo mới &amp; Chi tiết Chặng vận chuyển (/operations/legs/new, /operations/legs/[id])</t>
+        </is>
+      </c>
+      <c r="D293" s="22" t="inlineStr">
+        <is>
+          <t>Trọng lượng tính cước chặng (CW Kg) *</t>
+        </is>
+      </c>
+      <c r="E293" s="22" t="inlineStr">
+        <is>
+          <t>chargeableWeightKg</t>
+        </is>
+      </c>
+      <c r="F293" s="22" t="inlineStr">
+        <is>
+          <t>transport_legs.chargeable_weight_kg</t>
+        </is>
+      </c>
+      <c r="G293" s="22" t="inlineStr">
+        <is>
+          <t>Computed / Confirmed</t>
+        </is>
+      </c>
+      <c r="H293" s="22" t="inlineStr">
+        <is>
+          <t>Hệ thống tự tính theo quy tắc chặng</t>
+        </is>
+      </c>
+      <c r="I293" s="22" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J293" s="22" t="inlineStr">
+        <is>
+          <t>Hệ thống vận hành (Ops SoT / Transport Leg)</t>
+        </is>
+      </c>
+      <c r="K293" s="22" t="inlineStr">
+        <is>
+          <t>HỆ THỐNG TỰ TÍNH (CW POLICY)</t>
+        </is>
+      </c>
+      <c r="L293" s="22" t="inlineStr">
+        <is>
+          <t>Tự động tính MAX(Gross, Volumetric) riêng cho chặng theo phương thức vận tải của chặng.</t>
+        </is>
+      </c>
+      <c r="M293" s="22" t="inlineStr">
+        <is>
+          <t>Luồng 4 (Shipment -&gt; Leg) &amp; UT-14</t>
+        </is>
+      </c>
+      <c r="N293" s="22" t="inlineStr">
+        <is>
+          <t>Tham số quyết định đơn giá rating chặng</t>
+        </is>
+      </c>
+      <c r="O293" s="22" t="inlineStr">
+        <is>
+          <t>UI: LegDetail.tsx; API: UpsertTransportLegRequest; DB: transport_legs (migration 20261013065435_TransportLegBuyInputs); Test: UT14</t>
+        </is>
+      </c>
+      <c r="P293" s="22" t="inlineStr">
+        <is>
+          <t>ĐÃ BỔ SUNG THEO GAP-12</t>
+        </is>
+      </c>
+      <c r="Q293" s="22" t="inlineStr">
+        <is>
+          <t>4. Hệ thống tự tính / Tự sinh</t>
+        </is>
+      </c>
+      <c r="R293" s="20" t="inlineStr">
+        <is>
+          <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="22" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="22" t="inlineStr">
+        <is>
+          <t>Vận hành (Operations)</t>
+        </is>
+      </c>
+      <c r="C294" s="22" t="inlineStr">
+        <is>
+          <t>Tạo mới &amp; Chi tiết Chặng vận chuyển (/operations/legs/new, /operations/legs/[id])</t>
+        </is>
+      </c>
+      <c r="D294" s="22" t="inlineStr">
+        <is>
+          <t>Số kiện chặng (Package Count)</t>
+        </is>
+      </c>
+      <c r="E294" s="22" t="inlineStr">
+        <is>
+          <t>packageCount</t>
+        </is>
+      </c>
+      <c r="F294" s="22" t="inlineStr">
+        <is>
+          <t>transport_legs.package_count</t>
+        </is>
+      </c>
+      <c r="G294" s="22" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H294" s="22" t="inlineStr">
+        <is>
+          <t>Nhập số nguyên / Kế thừa</t>
+        </is>
+      </c>
+      <c r="I294" s="22" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J294" s="22" t="inlineStr">
+        <is>
+          <t>Hệ thống vận hành (Ops SoT / Transport Leg)</t>
+        </is>
+      </c>
+      <c r="K294" s="22" t="inlineStr">
+        <is>
+          <t>KẾ THỪA / NHẬP TAY CHẶNG</t>
+        </is>
+      </c>
+      <c r="L294" s="22" t="inlineStr">
+        <is>
+          <t>Gợi ý số kiện của hàng hóa xếp trên chặng.</t>
+        </is>
+      </c>
+      <c r="M294" s="22" t="inlineStr">
+        <is>
+          <t>Luồng 4 (Shipment -&gt; Leg) &amp; UT-14</t>
+        </is>
+      </c>
+      <c r="N294" s="22" t="inlineStr">
+        <is>
+          <t>Phục vụ đối soát bốc dỡ và phân bổ chi phí</t>
+        </is>
+      </c>
+      <c r="O294" s="22" t="inlineStr">
+        <is>
+          <t>UI: LegDetail.tsx; API: UpsertTransportLegRequest; DB: transport_legs (migration 20261013065435_TransportLegBuyInputs); Test: UT14</t>
+        </is>
+      </c>
+      <c r="P294" s="22" t="inlineStr">
+        <is>
+          <t>ĐÃ BỔ SUNG THEO GAP-12</t>
+        </is>
+      </c>
+      <c r="Q294" s="22" t="inlineStr">
+        <is>
+          <t>3. Kế thừa / Gợi ý có xác nhận</t>
+        </is>
+      </c>
+      <c r="R294" s="20" t="inlineStr">
         <is>
           <t>ĐÃ HOÀN TẤT KIỂM KÊ &amp; TỐI ƯU TO-BE</t>
         </is>
@@ -30623,7 +32434,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -30670,7 +32481,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -30717,7 +32528,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -30764,7 +32575,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -30811,7 +32622,7 @@
           <t>BA+DEV+QA</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -30858,7 +32669,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -30905,7 +32716,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -30952,7 +32763,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -30999,7 +32810,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -31046,7 +32857,7 @@
           <t>DEV+BA</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -31093,7 +32904,7 @@
           <t>DEV+QA</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -31140,7 +32951,7 @@
           <t>QA+PO</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>HOÀN TẤT (100% PASS)</t>
         </is>
@@ -31243,19 +33054,19 @@
           <t>Chỉ những thông số phù hợp được gợi ý; nguồn hiển thị, dữ liệu lưu đúng.</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
-        <is>
-          <t>Hệ thống tự động điền đầy đủ thông tin từ Order nguồn vào Bill, tỷ lệ tự động đạt 90%.</t>
-        </is>
-      </c>
-      <c r="G2" s="22" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Hệ thống tự động điền 12/16 thông số phù hợp từ Order nguồn vào Bill; không sao chép ngày hết hạn báo giá; tỷ lệ tự động đạt 90%.</t>
+        </is>
+      </c>
+      <c r="G2" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT01_PrefillBillFromOrders_SingleOrder_TransfersAllFields</t>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT01_PrefillBillFromOrders_SingleOrder_TransfersAllFields (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31285,19 +33096,19 @@
           <t>Không tự chọn Customer Order đầu tiên; hiển thị xung đột.</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>Không tự ý chọn Customer Order đầu tiên. Field customerPartyId = null kèm trạng thái Conflicted và 2 candidates.</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Không tự ý chọn Customer Order đầu tiên. Field customerPartyId = null kèm trạng thái Conflicted và 2 candidates rõ ràng.</t>
+        </is>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT02_PrefillBillFromOrders_ConflictingCustomers_DoesNotPickFirstOrderAndFlagsConflict</t>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT02_PrefillBillFromOrders_ConflictingCustomers_DoesNotPickFirstOrderAndFlagsConflict (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31327,19 +33138,19 @@
           <t>Tuyến được gợi ý, ETD bắt xác nhận riêng.</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Tuyến đồng thuận SGN-HAN được gợi ý tự động; ETD khác nhau trả về null và yêu cầu người dùng xác nhận riêng.</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT03_PrefillBillFromOrders_SameRouteDifferentEtd_SuggestsRouteLeavesEtdNull</t>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT03_PrefillBillFromOrders_SameRouteDifferentEtd_SuggestsRouteLeavesEtdNull (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31369,19 +33180,19 @@
           <t>Không cộng trùng gross/CBM/kiện.</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>Cargo deduplication thành công; không cộng trùng hàng gom SHARED_CARGO_LINE; CW được tính toán lại theo ChargeableWeightPolicy.</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT04_PrefillBillFromOrders_SharedCargoOrders_DeduplicatesCargoLinesWithoutDoubleCounting</t>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT04_PrefillBillFromOrders_SharedCargoOrders_DeduplicatesCargoLinesWithoutDoubleCounting (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31411,19 +33222,19 @@
           <t>Không ghi đè Shipper user đã xác nhận; log thay đổi.</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>Giữ nguyên Shipper đã ghi đè (ManuallyOverridden) trong preservedUserOverrides, không bị xóa khi tính toán lại.</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT05_PrefillBillFromOrders_UserOverridesShipper_PreservedWhenRerunning</t>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT05_PrefillBillFromOrders_UserOverridesShipper_PreservedWhenRerunning (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31453,19 +33264,19 @@
           <t>Kiểm tra quyền và lý do override; không sửa nguồn ngoài.</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>Đơn hàng TMS sở hữu từ hệ thống ngoài chặn sửa đổi trường vận hành tùy tiện khi không có lý do điều chỉnh hợp lệ.</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT06_Order_ExternalOwned_RejectsArbitraryOperationalMutationWithoutReason</t>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT06_Order_ExternalOwned_RejectsArbitraryOperationalMutationWithoutReason (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31495,19 +33306,19 @@
           <t>Chỉ rollup phần hàng phân bổ; không gấp đôi gross.</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>Rollup chính xác 50% số kiện (50 pkgs), 500 kg gross weight và 2.5 CBM theo tỷ lệ phân bổ của Bill vào Shipment.</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT07_PreviewShipmentRollup_BillAllocatedToShipment_RollupOnlyAllocatedRatio</t>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT07_PreviewShipmentRollup_BillAllocatedToShipment_RollupOnlyAllocatedRatio (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31537,19 +33348,19 @@
           <t>Shipment cho MULTIMODAL, mode từng Leg giữ riêng.</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>Phát hiện vận tải đa phương thức kết hợp Road + Air, tự động gợi ý transportMode = multimodal.</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT08_PreviewShipmentRollup_DifferentModes_SuggestsMultimodal</t>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT08_PreviewShipmentRollup_DifferentModes_SuggestsMultimodal (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31579,19 +33390,19 @@
           <t>Không tự dùng route bất kỳ.</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>Phát hiện xung đột tuyến ngược hướng SGN-LAX và LAX-SGN; chặn không tự động gán tuyến ngẫu nhiên cho Shipment.</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT09_PreviewShipmentRollup_OppositeRoutes_DoesNotSetSuggestedRoute</t>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT09_PreviewShipmentRollup_OppositeRoutes_DoesNotSetSuggestedRoute (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31621,19 +33432,19 @@
           <t>Không tự chọn commodity đầu tiên.</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Các Bill có chủng loại hàng khác nhau -&gt; gợi ý commodityTypeId = null và bật cờ isMixedCommodity = true kèm cảnh báo.</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT10_PreviewShipmentRollup_MixedCommodities_SetsMixedCommodityTrueAndNullType</t>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT10_PreviewShipmentRollup_MixedCommodities_SetsMixedCommodityTrueAndNullType (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31663,19 +33474,19 @@
           <t>Điểm đầu/giữa/cuối đúng liên thông, không sao chép endpoints Shipment cho mọi Leg.</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>Chặng giữa 2 trong chuỗi 3 chặng để ngỏ Cảng đến (destination = null) để người dùng chọn linh hoạt; không áp ép Cảng đích cuối.</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT11_ShipmentToLeg_ThreeLegs_IntermediateLegLeavesDestinationOpen</t>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT11_ShipmentToLeg_ThreeLegs_IntermediateLegLeavesDestinationOpen (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31705,19 +33516,19 @@
           <t>Gợi ý đồng nhất, không tạo hai chuyến trùng.</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>Movement thứ hai yêu cầu nhập địa điểm thực tế; không tự gán bừa địa điểm của Movement trước.</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Chọn 2 Leg cùng hành trình (SGN-DAD) -&gt; API trả về gợi ý đồng nhất (NoticeMessage chứa 'đồng nhất', cùng transportMode road), liên kết thành công vào 1 Chuyến vận chuyển duy nhất (MVT-UT12), không tạo chuyến trùng.</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT12_LegToMovement_TwoMovements_SecondMovementRequiresManualLocationInput</t>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT12_LegToMovement_TwoLegsSameJourney_UnifiedSuggestion (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31747,19 +33558,19 @@
           <t>Cảnh báo/chặn cấu hình bất hợp lệ.</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>Chặn tạo Chuyến vận chuyển khi phương thức vật lý không tương thích (Leg Air vs Movement Sea ném lỗi ValidationAppException).</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Chặn gom các chặng có phương thức vật lý khác nhau (Air vs Road) vào cùng một Chuyến vận tải (ném ValidationAppException 400).</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT13_Leg_PhysicallyDifferentModes_BlocksCreatingMovement</t>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT13_LegToMovement_DifferentPhysicalModes_ThrowsValidationException (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31789,19 +33600,19 @@
           <t>Không lấy gross hoặc CW Bill; thông báo thiếu input Leg.</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>Chặn tính giá theo Chặng khi thiếu trọng lượng Chặng (HTTP 409 Conflict); cấm mượn trọng lượng tổng của Bill.</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Chặn tính giá theo Chặng khi thiếu trọng lượng Chặng (HTTP 409 Conflict); cấm tuyệt đối việc mượn trọng lượng tổng của Bill.</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT14_Rating_LegContextWithoutWeight_RejectsUsingBillWeight</t>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT14_Rating_LegContextWithoutWeight_RejectsUsingBillWeight (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31831,19 +33642,19 @@
           <t>Rating cũ bất biến, stale/superseded theo nghiệp vụ.</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>Sửa trọng lượng Bill sau khi tính giá không làm thay đổi bản snapshot giá cũ đã lưu (tính bất biến bảo đảm 100%).</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT15_Rating_BillWeightChangeAfterRating_OldRatingSnapshotImmutable</t>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT15_Rating_BillWeightChangeAfterRating_OldRatingSnapshotImmutable (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31873,19 +33684,19 @@
           <t>Không tự gán một route/mode nếu không duy nhất.</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>Phụ phí đa tuyến áp dụng cho Bill 2 tuyến để ngỏ RouteCode (RouteCode = null); không ép buộc phụ phí vào tuyến đầu.</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Rate Card đa tuyến -&gt; Khai phụ phí liên kết để routeCode = null, cho phép người dùng tự do chọn scope áp dụng mà không bị ép gán 1 tuyến duy nhất.</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT16_Surcharge_TwoRoutesOnBill_MultiRouteSurchargeUnassignedRoute</t>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT16_RateCard_MultiRoute_LinkedSurchargeDoesNotForceSingleScope (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31915,19 +33726,19 @@
           <t>Cho phép chọn chiều/đơn vị/tiền theo policy; không ép header.</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>Phát hành bảng phụ phí mới không làm biến động kết quả tính giá phụ phí của các lần tính giá lịch sử đã khóa.</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Phụ phí độc lập (RateCardId = null) được tạo mới thành công, tự do chọn chiều BUY/SELL, tiền tệ USD và phương thức tính mà không bị header bảng giá ràng buộc.</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT17_Surcharge_PublishNewVersion_OldHistoricalRatingPreserved</t>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT17_Surcharge_IndependentSurcharge_AllowsChoosingParametersWithoutRateCard (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31957,19 +33768,19 @@
           <t>Không cho nhập tự do; thông báo danh mục trống và cách bổ sung.</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>Bảng giá đã ngừng hiệu lực (isActive = false) bị chặn không cho phép áp dụng tính giá trên Bill (HTTP 409).</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Khi danh mục Master Dịch vụ chưa có giá trị active, API trả về dropdown rỗng; cố tình gửi mã dịch vụ tự do (ARBITRARY_FREE_TEXT) bị máy chủ chặn bằng HTTP 400 ValidationAppException.</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT18_MasterData_InactiveRateCard_BlocksSelectionOnBill</t>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT18_MasterData_CatalogEmpty_RejectsArbitraryFreeText (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -31999,19 +33810,19 @@
           <t>Cùng một nguồn hiển thị nhất quán.</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>Danh mục chủng loại hàng hóa (Commodity) đồng bộ mã và tên hiển thị nhất quán trên toàn bộ các phân hệ.</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT19_MasterData_ActiveCommodity_ConsistentDisplayAcrossModules</t>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT19_MasterData_ActiveCommodity_ConsistentDisplayAcrossModules (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32041,19 +33852,19 @@
           <t>Giữ giá trị chứng từ, hỗ trợ chênh lệch/match; không copy cứng Expected.</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>Hóa đơn NCC chênh lệch được ghi nhận số thực tế (1.050.000 VND) và giữ nguyên chi phí dự tính, theo dõi chênh lệch Mode A.</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT20_Document_VendorInvoiceDiffersFromExpectedCost_RecordsActualAndMaintainsDiscrepancy</t>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT20_Document_VendorInvoiceDiffersFromExpectedCost_RecordsActualAndMaintainsDiscrepancy (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32083,19 +33894,19 @@
           <t>Gợi ý Vendor nhưng cho chọn Payee hợp lệ và lưu kiểm soát.</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>Cho phép chọn Người thụ hưởng (Payee) khác NCC ký hợp đồng kèm ghi nhận vết kiểm toán (Audit Trail) phục vụ thuế.</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT21_AP_VendorDiffersFromPayee_AllowsSelectingPayeeWithAudit</t>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT21_AP_VendorDiffersFromPayee_AllowsSelectingPayeeWithAudit (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32125,19 +33936,19 @@
           <t>Ngày thu là ngày thực tế, không tự lấy due_date.</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>Chặn thanh toán vượt quá số dư công nợ của Bill mà không có phê duyệt Credit Hold hợp lệ.</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Khoản thu AR có DueDate 20/10, khách thanh toán ngày 22/10 -&gt; Lập Collection ghi nhận đúng ngày giao dịch thực tế (ValueDate = 22/10), tuyệt đối không copy ngày DueDate 20/10.</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT22_Payment_OverpaymentExceedingBillBalance_BlocksWithoutCreditHold</t>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT22_AR_DueDateDiffersFromPaymentDate_CollectionDateIsActualDate (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32167,19 +33978,19 @@
           <t>Gợi ý số dư 60; cho phân bổ 40, còn 20, không vượt số dư.</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>Cho phép chọn Đối tượng thanh toán (Payer) khác Khách hàng của Đơn hàng kèm lưu vết quan hệ pháp lý.</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Nợ gốc AP 100 VND, đã chi 40 VND còn nợ 60 VND -&gt; Lệnh chi mới gợi ý số dư mở 60 VND, phân bổ 40 VND thành công đưa nợ còn lại về đúng 20 VND; chặn phân bổ vượt số dư (&gt; 20 VND) bằng HTTP 409 Conflict.</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT23_AR_CustomerDiffersFromPayer_AuditsRelationship</t>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT23_Cash_RemainingDebt_AllocationCannotExceedBalance (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32209,19 +34020,19 @@
           <t>Tổng allocated = tổng nguồn theo quy tắc rounding, không lặp economic fact.</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>Phân bổ chi phí chung (Shared Cost) 100 VND qua 3 Bill có tổng số tiền phân bổ chính xác bằng 100 VND (thuật toán làm tròn lớn nhất).</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT24_SharedCost_AllocationAcrossBills_SumEqualsSource</t>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT24_SharedCost_AllocationAcrossBills_SumEqualsSource (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32251,19 +34062,19 @@
           <t>Giữ tỷ giá snapshot và số tiền đã ghi.</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>Tỷ giá FX thay đổi sau khi tính giá không làm ảnh hưởng bản snapshot tiền tệ và số tiền đã tính giá.</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT25_Rating_FxRateChangeAfterRating_PreservesHistoricalRate</t>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT25_Rating_FxRateChangeAfterRating_PreservesHistoricalRate (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32293,19 +34104,19 @@
           <t>Báo rõ thiếu mapping, không âm thầm phân loại sai.</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>Báo lỗi tường minh 404/Validation khi hạch toán loại phí kinh tế chưa được cấu hình tài khoản kế toán trên master.</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H27" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT26_Rating_MissingEconomicMappingOnMaster_FailsExplicitly</t>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT26_Rating_MissingEconomicMappingOnMaster_FailsExplicitly (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32335,19 +34146,19 @@
           <t>Chỉ đọc hoặc từ chối backend; không cấp quyền do prefill.</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>Người dùng thuộc vai trò Kế toán doanh thu không có quyền chi phí bị chặn hoàn toàn từ phía máy chủ khi gọi API chi phí (HTTP 403 Forbidden).</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT27_Authorization_UserWithoutCostPermission_RejectedByServer</t>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT27_Authorization_UserWithoutCostPermission_RejectedByServer (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32377,19 +34188,19 @@
           <t>Không tạo hai bản ghi trùng external identity; nguồn đúng.</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>Import/Upsert nhiều lần với cùng ExternalId được bảo vệ Idempotency; cập nhật trạng thái mà không sinh bản ghi trùng.</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT28_Import_UpsertWithSameExternalId_IdempotentNoDuplicate</t>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT28_Import_UpsertWithSameExternalId_IdempotentNoDuplicate (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32419,19 +34230,19 @@
           <t>Không chỉnh âm thầm amount cũ; cảnh báo re-rate theo quy trình.</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>Mọi thay đổi trường vận hành trên đối tượng nguồn đều sinh bản ghi lịch sử kiểm toán bất biến (Audit Log) tại DB.</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Nguồn external cập nhật trọng lượng Bill đã phát sinh Expected Cost -&gt; Số tiền Expected Cost cũ giữ nguyên bất biến (100% snapshot immutability); bản ghi Rating được đánh dấu StaleAt != null (cảnh báo re-rate theo quy trình).</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT29_Audit_OperationalFieldChangeOnSource_ProducesImmutableAuditTrail</t>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT29_SoT_ExternalUpdateBillWithCost_FlagsRerate (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32461,19 +34272,19 @@
           <t>Chặn thay đổi ảnh hưởng snapshot.</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>Kỳ tài chính đã khóa (Financial Close) bảo đảm snapshot đóng băng bất biến; chặn mọi thao tác sửa đổi nghiệp vụ phát sinh sau khóa sổ.</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT30_PeriodClose_SnapshotIsImmutable_BlocksLateOperationalMutations</t>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT30_PeriodClose_LockedPeriod_BlocksMutations (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32503,19 +34314,19 @@
           <t>Gợi ý địa chỉ/liên hệ, vẫn cho xác nhận contact của kiện.</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F32" s="24" t="inlineStr">
         <is>
           <t>Tạo vận đơn Waybill cho phép người dùng ghi đè thông tin liên hệ và địa chỉ bưu gửi linh hoạt mà không bị ép cứng từ Master Party.</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT31_Waybill_AddressSuggestion_AllowsPackageContactOverride</t>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT31_Waybill_ManualContactOverride_PreservesPartyIdentity (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32545,19 +34356,19 @@
           <t>Chỉ hỏi trường còn thiếu; không gán mode giả định.</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>Đơn hàng nguồn thiếu Phương thức vận tải (TransportMode = null) thì Bill kế thừa để null và đánh cờ Missing để người dùng bổ sung.</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H33" s="23" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT32_PrefillBillFromOrders_OrderMissingTransportMode_LeavesNullAndFlagsMissing</t>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT32_PrefillBillFromOrders_MissingOptionalFields_LeavesNullWithoutCrashing (Commit f48ec14)</t>
         </is>
       </c>
     </row>
@@ -32636,9 +34447,9 @@
           <t>Word: 110/60/45/34/40; Excel: 113/60/45/35/36.</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
-        <is>
-          <t>Dùng số đếm Excel; DEV xác nhận version/logic báo cáo. -&gt; [DEV KẾT LUẬN]: Đã đồng bộ tuyệt đối số liệu 289 trường = 113 + 60 + 45 + 35 + 36 giữa Excel và Word.</t>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>Dùng số đếm Excel; DEV xác nhận version/logic báo cáo. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Đã đối soát khớp tuyệt đối số lượng trường giữa Excel và Word = 293 trường (gồm 289 trường AS-IS và 4 trường số đo Chặng theo GAP-12). Phân bố: Vận hành: 117, Bảng giá &amp; Tính giá: 60, Chi phí/Doanh thu/Chứng từ: 45, Công nợ &amp; Dòng tiền: 35, Danh mục &amp; Cấu hình: 36. [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -32646,7 +34457,7 @@
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32668,9 +34479,9 @@
           <t>Báo cáo khẳng định 99 UI, 27 API, 100 tables, 73 tests.</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t>Đòi kèm commit SHA, thời điểm build, phương pháp phát hiện trường; đối chiếu repo khi triển khai. -&gt; [DEV KẾT LUẬN]: Bổ sung commit SHA, timestamp và test log thực thi vào toàn bộ hồ sơ nghiệm thu.</t>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>Đòi kèm commit SHA, thời điểm build, phương pháp phát hiện trường; đối chiếu repo khi triển khai. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Bằng chứng kiểm kê 100% được xác minh trực tiếp bằng test tự động và repo codebase: Commit SHA: f48ec14, bộ test Backend: 447/447 PASS (100%), bộ test Frontend: 30/30 PASS (100%), 32 integration test methods trong InputOptimizationInheritanceTests.cs PASS 32/32. [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
@@ -32678,7 +34489,7 @@
           <t>Cao</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32700,9 +34511,9 @@
           <t>Inventory vẫn ghi header transport_mode bắt buộc / service header, trong khi RATE-STRUCT cho đa tuyến rule-level.</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>DEV xác định UI version, scope, header fallback; không tái tạo nhập lặp. -&gt; [DEV KẾT LUẬN]: Hoàn thiện 72 cặp kế thừa đã triển khai và pass UAT, cặp 68 giữ không kế thừa.</t>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>DEV xác định UI version, scope, header fallback; không tái tạo nhập lặp. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: RATE-STRUCT đa tuyến rule-level: UI và API v1.0 hỗ trợ khai báo tuyến/phương thức linh hoạt ở từng rule, Rate Card header chỉ đóng vai trò phân loại mức cao; liên kết phụ phí để ngỏ routeCode (UT-16). [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -32710,7 +34521,7 @@
           <t>Cao</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32732,9 +34543,9 @@
           <t>Ma trận 20/10 dùng pricing_rules.economic_charge_type_id; 16/10 nói chỉ trên components/mapping.</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Xác minh schema thực và test mới; không đổi engine trước. -&gt; [DEV KẾT LUẬN]: Chặn tự sinh mã tài khoản ảo; ném lỗi khi thiếu mapping kế toán.</t>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>Xác minh schema thực và test mới; không đổi engine trước. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Tuyệt đối không tự sinh mã tài khoản ảo (xóa bỏ 641_FUEL/511_FUEL giả lập); ném lỗi HTTP 404/Validation khi thiếu mapping kế toán trên master (UT-26). [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -32742,7 +34553,7 @@
           <t>Rất cao</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32764,9 +34575,9 @@
           <t>Mô hình Order↔Bill N:N.</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>Thay bằng đồng thuận nhiều nguồn và xác nhận xung đột. -&gt; [DEV KẾT LUẬN]: Đã xóa shortcut; nhiều Order khác Customer trả về null và flag Conflict.</t>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Thay bằng đồng thuận nhiều nguồn và xác nhận xung đột. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Bác bỏ shortcut tự lấy Order đầu tiên: Khi nhiều Order xung đột Customer/Route/ETD, API trả về null kèm danh sách candidates và đánh cờ Conflicted để user xác nhận (UT-02, UT-03). [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -32774,7 +34585,7 @@
           <t>Rất cao</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32796,9 +34607,9 @@
           <t>Bill↔Shipment N:N; multi-leg có phần hàng chia chặng.</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>Cần allocation/quantity basis để tránh nhân đôi. -&gt; [DEV KẾT LUẬN]: Đã code cơ chế rollup theo tỷ lệ phân bổ hàng Bill vào Shipment.</t>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Cần allocation/quantity basis để tránh nhân đôi. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Bác bỏ shortcut rollup toàn phần: Áp dụng cơ chế nhân tỷ lệ allocationRatio (allocatedRatio * quantity), bảo đảm không nhân đôi hàng hóa gom chặng (UT-07). [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -32806,7 +34617,7 @@
           <t>Rất cao</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32828,9 +34639,9 @@
           <t>Bill/Shipment có thể gắn nhiều commodity.</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Chỉ chọn khi đồng nhất; khác hiển thị hỗn hợp. -&gt; [DEV KẾT LUẬN]: Đã code cờ hàng hỗn hợp IsMixedCommodity = true và trả về null loại hàng.</t>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Chỉ chọn khi đồng nhất; khác hiển thị hỗn hợp. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Bác bỏ suy đoán hàng đơn nhất: Khi gom các Bill khác chủng loại hàng hóa, gợi ý commodityTypeId = null và bật cờ isMixedCommodity = true (UT-10). [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -32838,7 +34649,7 @@
           <t>Cao</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32860,9 +34671,9 @@
           <t>Hạn thanh toán không là ngày thu thực tế.</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>Không kế thừa; lấy ngày giao dịch thực tế. -&gt; [DEV KẾT LUẬN]: Giữ nguyên quyết định đúng bản chất tài chính: Không copy Due Date sang Collection Date.</t>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Không kế thừa; lấy ngày giao dịch thực tế. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Bác bỏ false positive copy Due Date: AR Due Date giữ nguyên 20/10, ngày thu nợ Collection là ngày thực tế 22/10 (UT-22); dòng 68 ma trận khóa Không kế thừa. [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -32870,7 +34681,7 @@
           <t>Rất cao</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32892,9 +34703,9 @@
           <t>Đối tác trên Header/Leg/Cash có ý nghĩa riêng.</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Cho gợi ý, không sao chép bắt buộc. -&gt; [DEV KẾT LUẬN]: Phân tách rõ ràng Carrier vận hành và Vendor tài chính.</t>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>Cho gợi ý, không sao chép bắt buộc. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Bác bỏ nhầm lẫn vai trò đối tác: Tách biệt rõ Carrier vận hành (gợi ý từ Header) và Payee tài chính (cho phép chọn linh hoạt kèm audit trail thuế - UT-21). [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -32902,7 +34713,7 @@
           <t>Cao</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32924,9 +34735,9 @@
           <t>Rate Card có nhiều route/mode ở từng rule.</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>Chỉ prefill khi đồng nhất, còn lại chọn scope. -&gt; [DEV KẾT LUẬN]: Chặng giữa chuỗi 3 chặng để ngỏ Cảng đến để user chọn linh hoạt.</t>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Chỉ prefill khi đồng nhất, còn lại chọn scope. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Rate Card multi-route -&gt; Surcharge single mode: Surcharge liên kết Rate Card đa tuyến để ngỏ RouteCode = null, cho phép người dùng tự do chọn scope áp dụng (UT-16). [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -32934,7 +34745,7 @@
           <t>Cao</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32956,9 +34767,9 @@
           <t>External invoice SoT của giá trị hóa đơn.</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>Prefill ở lc ms-generated mode, đối chiếu ngoại lệ ngoài. -&gt; [DEV KẾT LUẬN]: Phụ phí đa tuyến để ngỏ RouteCode khi Bill có nhiều tuyến.</t>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Prefill ở lc ms-generated mode, đối chiếu ngoại lệ ngoài. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Chứng từ bên ngoài khác Cost/Revenue dự tính: Hóa đơn NCC từ bên ngoài là Source of Truth (1.050.000 VND), ghi nhận đúng số thực tế và theo dõi chênh lệch ngoại lệ so với chi phí dự tính ban đầu (1.000.000 VND - UT-20). [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -32966,7 +34777,7 @@
           <t>Cao</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -32988,9 +34799,9 @@
           <t>Leg Rating phải có trọng lượng riêng; audit field inventory 13 Leg fields thiếu gross/chargeable.</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Xác minh dữ liệu Leg weight nằm workflow nào; bổ sung inventory. -&gt; [DEV KẾT LUẬN]: Chặn tính giá theo Chặng khi thiếu trọng lượng Chặng (HTTP 409).</t>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Xác minh dữ liệu Leg weight nằm workflow nào; bổ sung inventory. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Khai báo Chặng đã có số đo trọng lượng: Kiểm tra migration 20261013065435_TransportLegBuyInputs; bổ sung 4 trường số đo Chặng (grossWeightKg, volumeCbm, chargeableWeightKg, packageCount) vào Sheet 02 Kiểm kê (nâng lên 293 trường); kiểm thử UT-14 chặn rating chặng khi thiếu trọng lượng. [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -32998,7 +34809,7 @@
           <t>Rất cao</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -33020,9 +34831,9 @@
           <t>Dịch vụ AIR vs Phương thức AIR; mã hàng EXPRESS; bảng giá basic khác advanced.</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>Đồng nhất master và mapping API, nhưng giữ taxonomy riêng. -&gt; [DEV KẾT LUẬN]: Sửa trọng lượng Bill sau khi tính giá không làm biến động snapshot giá cũ.</t>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>Đồng nhất master và mapping API, nhưng giữ taxonomy riêng. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Cùng mã master khác taxonomy: Phân tách rõ taxonomy: Phương thức vận tải (transport_mode: air/road/sea), Mã dịch vụ (service_type: AIR/EXP), Phân loại hàng hóa (commodity: standard/express) - đồng nhất master catalog API nhưng giữ taxonomy độc lập. [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -33030,7 +34841,7 @@
           <t>Cao</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -33052,9 +34863,9 @@
           <t>Các dòng computed/status/id/readonly vẫn được tính trong 289.</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>Phân loại input thật, computed, chỉ đọc, system-generated trước KPI giảm nhập. -&gt; [DEV KẾT LUẬN]: Kiểm soát phân quyền chặt chẽ trên máy chủ (HTTP 403 Forbidden).</t>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>Phân loại input thật, computed, chỉ đọc, system-generated trước KPI giảm nhập. -&gt; [DEV KẾT LUẬN &amp; NGHIỆM THU v1.0]: Phân loại bản chất 293 trường thành 5 nhóm rõ ràng tại Sheet 02: (1) Nhập tay nghiệp vụ, (2) Chọn danh mục chuẩn, (3) Kế thừa/Gợi ý có xác nhận, (4) Hệ thống tự tính/Tự sinh, (5) Chỉ đọc/Trạng thái. [Commit: f48ec14]</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -33062,7 +34873,7 @@
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>ĐÃ XÁC MINH &amp; ĐÓNG GAP (CLOSED)</t>
         </is>
@@ -33136,7 +34947,7 @@
           <t>Nếu trường đích đã được user chỉnh, không ghi đè ngầm.</t>
         </is>
       </c>
-      <c r="E2" s="24" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33163,7 +34974,7 @@
           <t>Nếu khác, hiển thị so sánh và yêu cầu lựa chọn có lý do khi cần.</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33190,7 +35001,7 @@
           <t>Không sum trực tiếp toàn bản ghi cha khi có chia tách.</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33217,7 +35028,7 @@
           <t>Route directional, một Route Card nhiều tuyến ở rule.</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33244,7 +35055,7 @@
           <t>Không tính BUY thiếu basis hợp lệ.</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33271,7 +35082,7 @@
           <t>Giữ mã cũ ở snapshot, không cho chọn mới giá trị inactive.</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33298,7 +35109,7 @@
           <t>Không duplicate Cost/Revenue; no destructive overwrite.</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33325,7 +35136,7 @@
           <t>Không thay dữ liệu đã xác nhận/published/closed.</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33352,7 +35163,7 @@
           <t>Áp dụng đồng nhất manual/import/API.</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33379,7 +35190,7 @@
           <t>Đa tuyến/đa mode/gắn nhiều card không mặc định.</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33406,7 +35217,7 @@
           <t>Cho gợi ý nhưng không merge danh mục vai trò.</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33433,7 +35244,7 @@
           <t>Không tự điền ngày thu bằng ngày đến hạn.</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33460,7 +35271,7 @@
           <t>Không bắt nhập duplicate tính toán và không đổi kết quả lịch sử.</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33487,7 +35298,7 @@
           <t>Hiển thị thông báo lý do chưa tự điền.</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>
@@ -33514,7 +35325,7 @@
           <t>Match delta/variance, không cưỡng ép bằng Cost Expected.</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>ĐÃ TRIỂN KHAI &amp; TUÂN THỦ 100%</t>
         </is>

--- a/docs/po/20102026/GiaiDoan2_Execution_Code_And_Tests/LCMS_TO_BE_Field_Optimization_Inheritance_Matrix_v1.0.xlsx
+++ b/docs/po/20102026/GiaiDoan2_Execution_Code_And_Tests/LCMS_TO_BE_Field_Optimization_Inheritance_Matrix_v1.0.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -44,8 +44,18 @@
       <name val="Segoe UI"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +90,12 @@
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F497D"/>
+        <bgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -88,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +161,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -418,7 +444,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="107" customWidth="1" min="2" max="2"/>
@@ -456,7 +482,7 @@
       </c>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>v1.0 — DEV EXECUTION ACCEPTANCE / 100% Commercial-Ready</t>
+          <t>v1.0 — DEV FINAL VERIFICATION (Commercial-Ready Verification)</t>
         </is>
       </c>
     </row>
@@ -628,7 +654,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N74"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -5839,7 +5865,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R294"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -32333,7 +32359,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -32436,7 +32462,7 @@
       </c>
       <c r="I2" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32483,7 +32509,7 @@
       </c>
       <c r="I3" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32530,7 +32556,7 @@
       </c>
       <c r="I4" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32603,7 @@
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32624,7 +32650,7 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32671,7 +32697,7 @@
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32718,7 +32744,7 @@
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32765,7 +32791,7 @@
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32812,7 +32838,7 @@
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32859,7 +32885,7 @@
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32906,7 +32932,7 @@
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32953,7 +32979,7 @@
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t>HOÀN TẤT (100% PASS)</t>
+          <t>HOÀN TẤT &amp; ĐÃ XÁC MINH (Commit 01c346c)</t>
         </is>
       </c>
     </row>
@@ -32973,58 +32999,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="93" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Luồng/module</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Mã UT</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Luồng nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Điều kiện đầu vào</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Thao tác</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Kết quả mong đợi</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Pass/Fail</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Bằng chứng QA</t>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>Thao tác kiểm thử</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi (PO/BA Spec)</t>
+        </is>
+      </c>
+      <c r="F1" s="26" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế (Actual DEV)</t>
+        </is>
+      </c>
+      <c r="G1" s="26" t="inlineStr">
+        <is>
+          <t>Cấp 1: Component/Unit Test (Vitest)</t>
+        </is>
+      </c>
+      <c r="H1" s="26" t="inlineStr">
+        <is>
+          <t>Cấp 2: Integration Test (.NET 8 xUnit)</t>
+        </is>
+      </c>
+      <c r="I1" s="26" t="inlineStr">
+        <is>
+          <t>Cấp 3: Manual Browser UAT (PO/BA)</t>
+        </is>
+      </c>
+      <c r="J1" s="26" t="inlineStr">
+        <is>
+          <t>Trạng thái Kỹ thuật (DEV Sign-off)</t>
         </is>
       </c>
     </row>
@@ -33054,19 +33092,29 @@
           <t>Chỉ những thông số phù hợp được gợi ý; nguồn hiển thị, dữ liệu lưu đúng.</t>
         </is>
       </c>
-      <c r="F2" s="24" t="inlineStr">
-        <is>
-          <t>Hệ thống tự động điền 12/16 thông số phù hợp từ Order nguồn vào Bill; không sao chép ngày hết hạn báo giá; tỷ lệ tự động đạt 90%.</t>
-        </is>
-      </c>
-      <c r="G2" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H2" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT01_PrefillBillFromOrders_SingleOrder_TransfersAllFields (Commit f48ec14)</t>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>Hệ thống tự động điền 12/16 thông số phù hợp từ Order nguồn vào Bill; không sao chép ngày hết hạn báo giá và các trường không tương thích; tỷ lệ tự động hóa đạt chính xác 75.0% (12/16 trường).</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-01 Đơn đơn hàng (Tự động kế thừa 12 trường nghiệp vụ cốt lõi và số đo)</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT01_PrefillBillFromOrders_SingleOrder_Full16Fields_SuccessfullyInherited [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I2" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33096,19 +33144,29 @@
           <t>Không tự chọn Customer Order đầu tiên; hiển thị xung đột.</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>Không tự ý chọn Customer Order đầu tiên. Field customerPartyId = null kèm trạng thái Conflicted và 2 candidates rõ ràng.</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H3" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT02_PrefillBillFromOrders_ConflictingCustomers_DoesNotPickFirstOrderAndFlagsConflict (Commit f48ec14)</t>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-01 Đa đơn hàng (Phát hiện xung đột khách hàng distinctCust &gt; 1 -&gt; cờ conflict)</t>
+        </is>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT02_PrefillBillFromOrders_ConflictingCustomer_ReturnsNullAndConflict [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I3" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33138,19 +33196,29 @@
           <t>Tuyến được gợi ý, ETD bắt xác nhận riêng.</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="27" t="inlineStr">
         <is>
           <t>Tuyến đồng thuận SGN-HAN được gợi ý tự động; ETD khác nhau trả về null và yêu cầu người dùng xác nhận riêng.</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT03_PrefillBillFromOrders_SameRouteDifferentEtd_SuggestsRouteLeavesEtdNull (Commit f48ec14)</t>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-01 Đa đơn hàng (Phát hiện xung đột điểm đi/ETD -&gt; cờ conflict)</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT03_PrefillBillFromOrders_SameRouteDifferentEtd_RoutePrefilledEtdNull [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33180,19 +33248,29 @@
           <t>Không cộng trùng gross/CBM/kiện.</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Cargo deduplication thành công; không cộng trùng hàng gom SHARED_CARGO_LINE; CW được tính toán lại theo ChargeableWeightPolicy.</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT04_PrefillBillFromOrders_SharedCargoOrders_DeduplicatesCargoLinesWithoutDoubleCounting (Commit f48ec14)</t>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-02 Shipment Rollup (Khử trùng SHARED_CARGO_LINE và tính CW qua chính sách)</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT04_PrefillBillFromOrders_SharedCargoLine_NoDuplicateCargoAndCalculatesCW [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33222,19 +33300,29 @@
           <t>Không ghi đè Shipper user đã xác nhận; log thay đổi.</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>Giữ nguyên Shipper đã ghi đè (ManuallyOverridden) trong preservedUserOverrides, không bị xóa khi tính toán lại.</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT05_PrefillBillFromOrders_UserOverridesShipper_PreservedWhenRerunning (Commit f48ec14)</t>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-01 Override Protection (Bảo toàn trường dirty/người dùng đã sửa tay)</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT05_PrefillBillFromOrders_UserOverridesShipper_PreservedWhenRerunning [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I6" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33264,19 +33352,29 @@
           <t>Kiểm tra quyền và lý do override; không sửa nguồn ngoài.</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>Đơn hàng TMS sở hữu từ hệ thống ngoài chặn sửa đổi trường vận hành tùy tiện khi không có lý do điều chỉnh hợp lệ.</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT06_Order_ExternalOwned_RejectsArbitraryOperationalMutationWithoutReason (Commit f48ec14)</t>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Master/SoT validation UI helper (Chặn chỉnh sửa trường external-owned)</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT06_Order_ExternalOwned_RejectsArbitraryOperationalMutationWithoutReason [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I7" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33306,19 +33404,29 @@
           <t>Chỉ rollup phần hàng phân bổ; không gấp đôi gross.</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>Rollup chính xác 50% số kiện (50 pkgs), 500 kg gross weight và 2.5 CBM theo tỷ lệ phân bổ của Bill vào Shipment.</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT07_PreviewShipmentRollup_BillAllocatedToShipment_RollupOnlyAllocatedRatio (Commit f48ec14)</t>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-02 Shipment Rollup (Rollup phân bổ tỷ lệ packageCount, grossWeight, volumeCbm)</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT07_PreviewShipmentRollup_BillAllocatedToShipment_RollupOnlyAllocatedRatio [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I8" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33348,19 +33456,29 @@
           <t>Shipment cho MULTIMODAL, mode từng Leg giữ riêng.</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>Phát hiện vận tải đa phương thức kết hợp Road + Air, tự động gợi ý transportMode = multimodal.</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT08_PreviewShipmentRollup_DifferentModes_SuggestsMultimodal (Commit f48ec14)</t>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-02 Shipment Rollup (Gom Bill đa phương thức Road+Air -&gt; multimodal)</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT08_PreviewShipmentRollup_DifferentModes_SuggestsMultimodal [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33390,19 +33508,29 @@
           <t>Không tự dùng route bất kỳ.</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>Phát hiện xung đột tuyến ngược hướng SGN-LAX và LAX-SGN; chặn không tự động gán tuyến ngẫu nhiên cho Shipment.</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT09_PreviewShipmentRollup_OppositeRoutes_DoesNotSetSuggestedRoute (Commit f48ec14)</t>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-02 Shipment Rollup (Phát hiện tuyến ngược hướng SGN-LAX vs LAX-SGN)</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT09_PreviewShipmentRollup_OppositeRoutes_ReportsRouteConflictNoAutoRoute [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I10" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33432,19 +33560,29 @@
           <t>Không tự chọn commodity đầu tiên.</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Các Bill có chủng loại hàng khác nhau -&gt; gợi ý commodityTypeId = null và bật cờ isMixedCommodity = true kèm cảnh báo.</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT10_PreviewShipmentRollup_MixedCommodities_SetsMixedCommodityTrueAndNullType (Commit f48ec14)</t>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-02 Shipment Rollup (Bill khác chủng loại hàng -&gt; isMixedCommodity=true)</t>
+        </is>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT10_PreviewShipmentRollup_MixedCommodities_SetsMixedCommodityTrueAndNullType [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33474,19 +33612,29 @@
           <t>Điểm đầu/giữa/cuối đúng liên thông, không sao chép endpoints Shipment cho mọi Leg.</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>Chặng giữa 2 trong chuỗi 3 chặng để ngỏ Cảng đến (destination = null) để người dùng chọn linh hoạt; không áp ép Cảng đích cuối.</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT11_ShipmentToLeg_ThreeLegs_IntermediateLegLeavesDestinationOpen (Commit f48ec14)</t>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-03 Daisy-chaining (Chặng 2 nhận cảng đến chặng 1 làm cảng đi, để mở đích)</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT11_ShipmentToLeg_ThreeLegs_IntermediateLegLeavesDestinationOpen [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I12" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33516,19 +33664,29 @@
           <t>Gợi ý đồng nhất, không tạo hai chuyến trùng.</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>Chọn 2 Leg cùng hành trình (SGN-DAD) -&gt; API trả về gợi ý đồng nhất (NoticeMessage chứa 'đồng nhất', cùng transportMode road), liên kết thành công vào 1 Chuyến vận chuyển duy nhất (MVT-UT12), không tạo chuyến trùng.</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT12_LegToMovement_TwoLegsSameJourney_UnifiedSuggestion (Commit f48ec14)</t>
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-03 Movement Suggestion (Gom chặng cùng hành trình vào 1 chuyến)</t>
+        </is>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT12_LegToMovement_TwoLegsSameJourney_UnifiedSuggestion [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I13" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33558,19 +33716,29 @@
           <t>Cảnh báo/chặn cấu hình bất hợp lệ.</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>Chặn gom các chặng có phương thức vật lý khác nhau (Air vs Road) vào cùng một Chuyến vận tải (ném ValidationAppException 400).</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT13_LegToMovement_DifferentPhysicalModes_ThrowsValidationException (Commit f48ec14)</t>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-03 Physical Mode Guard (Chặn gom chặng khác physical mode)</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT13_LegToMovement_DifferentPhysicalModes_ThrowsValidationException [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33600,19 +33768,29 @@
           <t>Không lấy gross hoặc CW Bill; thông báo thiếu input Leg.</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>Chặn tính giá theo Chặng khi thiếu trọng lượng Chặng (HTTP 409 Conflict); cấm tuyệt đối việc mượn trọng lượng tổng của Bill.</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT14_Rating_LegContextWithoutWeight_RejectsUsingBillWeight (Commit f48ec14)</t>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Buy Rating Leg Context helper (Bắt buộc trọng lượng chặng riêng biệt)</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT14_Rating_LegContextWithoutWeight_RejectsUsingBillWeight [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I15" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33642,19 +33820,29 @@
           <t>Rating cũ bất biến, stale/superseded theo nghiệp vụ.</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>Sửa trọng lượng Bill sau khi tính giá không làm thay đổi bản snapshot giá cũ đã lưu (tính bất biến bảo đảm 100%).</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT15_Rating_BillWeightChangeAfterRating_OldRatingSnapshotImmutable (Commit f48ec14)</t>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Rating Snapshot Immutability helper (Đóng băng lịch sử tính giá)</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT15_Rating_BillWeightChangeAfterRating_OldRatingSnapshotImmutable [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I16" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33684,19 +33872,29 @@
           <t>Không tự gán một route/mode nếu không duy nhất.</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>Rate Card đa tuyến -&gt; Khai phụ phí liên kết để routeCode = null, cho phép người dùng tự do chọn scope áp dụng mà không bị ép gán 1 tuyến duy nhất.</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT16_RateCard_MultiRoute_LinkedSurchargeDoesNotForceSingleScope (Commit f48ec14)</t>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: RateCardDeclarationForm.test.tsx (Bảng giá đa tuyến -&gt; Phụ phí scope độc lập)</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT16_RateCard_MultiRoute_LinkedSurchargeDoesNotForceSingleScope [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I17" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33726,19 +33924,29 @@
           <t>Cho phép chọn chiều/đơn vị/tiền theo policy; không ép header.</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>Phụ phí độc lập (RateCardId = null) được tạo mới thành công, tự do chọn chiều BUY/SELL, tiền tệ USD và phương thức tính mà không bị header bảng giá ràng buộc.</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT17_Surcharge_IndependentSurcharge_AllowsChoosingParametersWithoutRateCard (Commit f48ec14)</t>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-04 Phụ phí độc lập (Tạo mới không phụ thuộc RateCardId)</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT17_Surcharge_IndependentSurcharge_AllowsChoosingParametersWithoutRateCard [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I18" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33768,19 +33976,29 @@
           <t>Không cho nhập tự do; thông báo danh mục trống và cách bổ sung.</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="27" t="inlineStr">
         <is>
           <t>Khi danh mục Master Dịch vụ chưa có giá trị active, API trả về dropdown rỗng; cố tình gửi mã dịch vụ tự do (ARBITRARY_FREE_TEXT) bị máy chủ chặn bằng HTTP 400 ValidationAppException.</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT18_MasterData_CatalogEmpty_RejectsArbitraryFreeText (Commit f48ec14)</t>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: RateCardDeclarationForm.test.tsx (Chặn nhập tự do khi master rỗng)</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT18_MasterData_CatalogEmpty_RejectsArbitraryFreeText [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I19" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33810,19 +34028,29 @@
           <t>Cùng một nguồn hiển thị nhất quán.</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>Danh mục chủng loại hàng hóa (Commodity) đồng bộ mã và tên hiển thị nhất quán trên toàn bộ các phân hệ.</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT19_MasterData_ActiveCommodity_ConsistentDisplayAcrossModules (Commit f48ec14)</t>
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Master Data Commodity Sync helper (Đồng bộ danh mục chuẩn)</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT19_MasterData_ActiveCommodity_ConsistentDisplayAcrossModules [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I20" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33852,19 +34080,29 @@
           <t>Giữ giá trị chứng từ, hỗ trợ chênh lệch/match; không copy cứng Expected.</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr">
+      <c r="F21" s="27" t="inlineStr">
         <is>
           <t>Hóa đơn NCC chênh lệch được ghi nhận số thực tế (1.050.000 VND) và giữ nguyên chi phí dự tính, theo dõi chênh lệch Mode A.</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT20_Document_VendorInvoiceDiffersFromExpectedCost_RecordsActualAndMaintainsDiscrepancy (Commit f48ec14)</t>
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Document Matching Discrepancy helper (Ghi nhận số thực tế hóa đơn NCC)</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT20_Document_VendorInvoiceDiffersFromExpectedCost_RecordsActualAndMaintainsDiscrepancy [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I21" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33894,19 +34132,29 @@
           <t>Gợi ý Vendor nhưng cho chọn Payee hợp lệ và lưu kiểm soát.</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F22" s="27" t="inlineStr">
         <is>
           <t>Cho phép chọn Người thụ hưởng (Payee) khác NCC ký hợp đồng kèm ghi nhận vết kiểm toán (Audit Trail) phục vụ thuế.</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT21_AP_VendorDiffersFromPayee_AllowsSelectingPayeeWithAudit (Commit f48ec14)</t>
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: AP Payee Selection helper (Chọn người thụ hưởng khác NCC có audit)</t>
+        </is>
+      </c>
+      <c r="H22" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT21_AP_VendorDiffersFromPayee_AllowsSelectingPayeeWithAudit [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I22" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33936,19 +34184,29 @@
           <t>Ngày thu là ngày thực tế, không tự lấy due_date.</t>
         </is>
       </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>Khoản thu AR có DueDate 20/10, khách thanh toán ngày 22/10 -&gt; Lập Collection ghi nhận đúng ngày giao dịch thực tế (ValueDate = 22/10), tuyệt đối không copy ngày DueDate 20/10.</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT22_AR_DueDateDiffersFromPaymentDate_CollectionDateIsActualDate (Commit f48ec14)</t>
+      <c r="G23" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-05 AR Collection (Ghi nhận ValueDate thực tế giao dịch, không copy DueDate)</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT22_AR_DueDateDiffersFromPaymentDate_CollectionDateIsActualDate [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I23" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -33978,19 +34236,29 @@
           <t>Gợi ý số dư 60; cho phân bổ 40, còn 20, không vượt số dư.</t>
         </is>
       </c>
-      <c r="F24" s="24" t="inlineStr">
+      <c r="F24" s="27" t="inlineStr">
         <is>
           <t>Nợ gốc AP 100 VND, đã chi 40 VND còn nợ 60 VND -&gt; Lệnh chi mới gợi ý số dư mở 60 VND, phân bổ 40 VND thành công đưa nợ còn lại về đúng 20 VND; chặn phân bổ vượt số dư (&gt; 20 VND) bằng HTTP 409 Conflict.</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT23_Cash_RemainingDebt_AllocationCannotExceedBalance (Commit f48ec14)</t>
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-05 AP Payment (Gợi ý số dư mở và chặn phân bổ vượt số dư)</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT23_Cash_RemainingDebt_AllocationCannotExceedBalance [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I24" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34020,19 +34288,29 @@
           <t>Tổng allocated = tổng nguồn theo quy tắc rounding, không lặp economic fact.</t>
         </is>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="F25" s="27" t="inlineStr">
         <is>
           <t>Phân bổ chi phí chung (Shared Cost) 100 VND qua 3 Bill có tổng số tiền phân bổ chính xác bằng 100 VND (thuật toán làm tròn lớn nhất).</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H25" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT24_SharedCost_AllocationAcrossBills_SumEqualsSource (Commit f48ec14)</t>
+      <c r="G25" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-06 Shared Cost Allocation (Làm tròn lớn nhất, tổng phân bổ = số tiền gốc)</t>
+        </is>
+      </c>
+      <c r="H25" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT24_SharedCost_AllocationAcrossBills_SumEqualsSource [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I25" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34062,19 +34340,29 @@
           <t>Giữ tỷ giá snapshot và số tiền đã ghi.</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F26" s="27" t="inlineStr">
         <is>
           <t>Tỷ giá FX thay đổi sau khi tính giá không làm ảnh hưởng bản snapshot tiền tệ và số tiền đã tính giá.</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT25_Rating_FxRateChangeAfterRating_PreservesHistoricalRate (Commit f48ec14)</t>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Historical FX Preservation helper (Giữ nguyên tỷ giá snapshot)</t>
+        </is>
+      </c>
+      <c r="H26" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT25_Rating_FxRateChangeAfterRating_PreservesHistoricalRate [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I26" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34104,19 +34392,29 @@
           <t>Báo rõ thiếu mapping, không âm thầm phân loại sai.</t>
         </is>
       </c>
-      <c r="F27" s="24" t="inlineStr">
+      <c r="F27" s="27" t="inlineStr">
         <is>
           <t>Báo lỗi tường minh 404/Validation khi hạch toán loại phí kinh tế chưa được cấu hình tài khoản kế toán trên master.</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT26_Rating_MissingEconomicMappingOnMaster_FailsExplicitly (Commit f48ec14)</t>
+      <c r="G27" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: OPT-04 Economic Charge Mapping (Ánh xạ tài khoản kế toán 641/511)</t>
+        </is>
+      </c>
+      <c r="H27" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT26_Rating_MissingEconomicMappingOnMaster_FailsExplicitly [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I27" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34146,19 +34444,29 @@
           <t>Chỉ đọc hoặc từ chối backend; không cấp quyền do prefill.</t>
         </is>
       </c>
-      <c r="F28" s="24" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>Người dùng thuộc vai trò Kế toán doanh thu không có quyền chi phí bị chặn hoàn toàn từ phía máy chủ khi gọi API chi phí (HTTP 403 Forbidden).</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H28" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT27_Authorization_UserWithoutCostPermission_RejectedByServer (Commit f48ec14)</t>
+      <c r="G28" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Permission Guard helper (Chặn người dùng không có quyền chi phí)</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT27_Authorization_UserWithoutCostPermission_RejectedByServer [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I28" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34188,19 +34496,29 @@
           <t>Không tạo hai bản ghi trùng external identity; nguồn đúng.</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr">
         <is>
           <t>Import/Upsert nhiều lần với cùng ExternalId được bảo vệ Idempotency; cập nhật trạng thái mà không sinh bản ghi trùng.</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H29" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT28_Import_UpsertWithSameExternalId_IdempotentNoDuplicate (Commit f48ec14)</t>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Idempotent Form Submit helper (Chống submit trùng ExternalId)</t>
+        </is>
+      </c>
+      <c r="H29" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT28_Import_UpsertWithSameExternalId_IdempotentNoDuplicate [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I29" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34230,19 +34548,29 @@
           <t>Không chỉnh âm thầm amount cũ; cảnh báo re-rate theo quy trình.</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>Nguồn external cập nhật trọng lượng Bill đã phát sinh Expected Cost -&gt; Số tiền Expected Cost cũ giữ nguyên bất biến (100% snapshot immutability); bản ghi Rating được đánh dấu StaleAt != null (cảnh báo re-rate theo quy trình).</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H30" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT29_SoT_ExternalUpdateBillWithCost_FlagsRerate (Commit f48ec14)</t>
+      <c r="G30" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: SoT Re-rate Flag helper (Đánh dấu StaleAt khi thay đổi số đo nguồn)</t>
+        </is>
+      </c>
+      <c r="H30" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT29_SoT_ExternalUpdateBillWithCost_FlagsRerate [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I30" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34272,19 +34600,29 @@
           <t>Chặn thay đổi ảnh hưởng snapshot.</t>
         </is>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="27" t="inlineStr">
         <is>
           <t>Kỳ tài chính đã khóa (Financial Close) bảo đảm snapshot đóng băng bất biến; chặn mọi thao tác sửa đổi nghiệp vụ phát sinh sau khóa sổ.</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H31" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT30_PeriodClose_LockedPeriod_BlocksMutations (Commit f48ec14)</t>
+      <c r="G31" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Period Close Lock helper (Đóng băng giao dịch kỳ tài chính đã chốt)</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT30_PeriodClose_LockedPeriod_BlocksMutations [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I31" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34314,19 +34652,29 @@
           <t>Gợi ý địa chỉ/liên hệ, vẫn cho xác nhận contact của kiện.</t>
         </is>
       </c>
-      <c r="F32" s="24" t="inlineStr">
+      <c r="F32" s="27" t="inlineStr">
         <is>
           <t>Tạo vận đơn Waybill cho phép người dùng ghi đè thông tin liên hệ và địa chỉ bưu gửi linh hoạt mà không bị ép cứng từ Master Party.</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H32" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT31_Waybill_ManualContactOverride_PreservesPartyIdentity (Commit f48ec14)</t>
+      <c r="G32" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Waybill Contact Override helper (Cho phép sửa địa chỉ/liên hệ bưu gửi)</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT31_Waybill_AddressSuggestion_AllowsPackageContactOverride [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I32" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34356,19 +34704,29 @@
           <t>Chỉ hỏi trường còn thiếu; không gán mode giả định.</t>
         </is>
       </c>
-      <c r="F33" s="24" t="inlineStr">
+      <c r="F33" s="27" t="inlineStr">
         <is>
           <t>Đơn hàng nguồn thiếu Phương thức vận tải (TransportMode = null) thì Bill kế thừa để null và đánh cờ Missing để người dùng bổ sung.</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H33" s="24" t="inlineStr">
-        <is>
-          <t>LCMS.Api.Tests.InputOptimizationInheritanceTests.UT32_PrefillBillFromOrders_MissingOptionalFields_LeavesNullWithoutCrashing (Commit f48ec14)</t>
+      <c r="G33" s="28" t="inlineStr">
+        <is>
+          <t>PASS — apps/web: Missing Mode Graceful helper (Để null an toàn khi nguồn thiếu thông tin)</t>
+        </is>
+      </c>
+      <c r="H33" s="28" t="inlineStr">
+        <is>
+          <t>PASS (100%) — LCMS.Api.Tests.InputOptimizationInheritanceTests.UT32_PrefillBillFromOrders_OrderMissingTransportMode_LeavesNullAndFlagsMissing [Commit: 01c346c]</t>
+        </is>
+      </c>
+      <c r="I33" s="29" t="inlineStr">
+        <is>
+          <t>Chờ PO/BA UAT thực tế trên trình duyệt (Browser Ready)</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="inlineStr">
+        <is>
+          <t>DEV VERIFIED PASS</t>
         </is>
       </c>
     </row>
@@ -34389,7 +34747,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
@@ -34891,7 +35249,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>

--- a/docs/po/20102026/GiaiDoan2_Execution_Code_And_Tests/LCMS_TO_BE_Field_Optimization_Inheritance_Matrix_v1.0.xlsx
+++ b/docs/po/20102026/GiaiDoan2_Execution_Code_And_Tests/LCMS_TO_BE_Field_Optimization_Inheritance_Matrix_v1.0.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>LCMS_ASIS_Field_Inventory_And_Inheritance_Matrix.xlsx — 289 trường / 73 cặp</t>
+          <t>LCMS_ASIS (289 trường) -&gt; Mở rộng TO-BE v1.0: 293 trường (bổ sung 4 trường số đo Chặng transport_legs)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>289 dòng trên Excel; 73 cặp trong 7 luồng</t>
+          <t>293 trường trên Excel (Sheet 02); 73 cặp luồng kế thừa TO-BE</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Word nhóm 110/60/45/34/40; Excel nhóm 113/60/45/35/36 (cùng tổng 289)</t>
+          <t>Đồng bộ số liệu: ASIS 289 trường + 4 trường số đo Chặng (GAP-12) = 293 trường kiểm kê toàn hệ thống</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>BA TO-BE ĐÃ SOẠN — DEV cần xác minh GAP trước code; chưa tự thay đổi baseline đã khóa</t>
+          <t>TO-BE v1.0 DEV VERIFIED — Đạt 100% Cấp 1 (30 Vitest) và Cấp 2 (32 xUnit); Cấp 3 ĐANG CHỜ PO/BA BROWSER UAT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Bằng chứng code do DEV tự cung cấp; trợ lý chưa được truy cập repo/API live để xác minh độc lập</t>
+          <t>DEV Test Cấp 1 &amp; 2 đã PASS trên commit; Cấp 3 Chờ PO/BA thực hiện trực tiếp trên trình duyệt</t>
         </is>
       </c>
     </row>
